--- a/Test Plan/Test Plan.xlsx
+++ b/Test Plan/Test Plan.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educwaac-my.sharepoint.com/personal/451102_edu_cwa_ac_uk/Documents/College Work/Assignments/Digital Portfolio/Creation/Test Plan/"/>
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -56,10 +56,10 @@
     <t>Success (Yes/No)</t>
   </si>
   <si>
+    <t>Checking if all links click</t>
+  </si>
+  <si>
     <t>Navigates to every link that is clicked on</t>
-  </si>
-  <si>
-    <t>Checking if all links click</t>
   </si>
   <si>
     <t>Check if website works on all devices under 768px</t>
@@ -76,7 +76,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,7 +512,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1BEF50-4814-4512-A0DE-435D547D7E8D}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="76.28515625" customWidth="1"/>
     <col min="3" max="3" width="45.28515625" customWidth="1"/>
@@ -520,7 +520,7 @@
     <col min="5" max="5" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -537,18 +537,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="70.5" customHeight="1">
       <c r="A2">
         <v>1.1000000000000001</v>
       </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="3" spans="1:5" ht="340.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="340.5" customHeight="1">
       <c r="A3">
         <v>1.2</v>
       </c>
@@ -562,12 +562,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="65.25" customHeight="1">
       <c r="A4">
         <v>1.3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="55.5" customHeight="1">
       <c r="A5">
         <v>1.4</v>
       </c>

--- a/Test Plan/Test Plan.xlsx
+++ b/Test Plan/Test Plan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educwaac-my.sharepoint.com/personal/451102_edu_cwa_ac_uk/Documents/College Work/Assignments/Digital Portfolio/Creation/Test Plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="8_{897BE40C-8596-4620-83A4-AA988CC80A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A8AA65C-629A-4610-B78B-74827EEE9A6B}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="8_{897BE40C-8596-4620-83A4-AA988CC80A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7E20AF2-BBEE-40B5-A0AF-B11DAB0474E3}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="345" windowWidth="16200" windowHeight="11430" xr2:uid="{1B0E92B5-A902-43FD-889A-9B0198319DB9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1B0E92B5-A902-43FD-889A-9B0198319DB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,8 +38,110 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="9">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="9">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+    <bk>
+      <rc t="1" v="5"/>
+    </bk>
+    <bk>
+      <rc t="1" v="6"/>
+    </bk>
+    <bk>
+      <rc t="1" v="7"/>
+    </bk>
+    <bk>
+      <rc t="1" v="8"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
   <si>
     <t>Test No.</t>
   </si>
@@ -56,27 +158,129 @@
     <t>Success (Yes/No)</t>
   </si>
   <si>
-    <t>Checking if all links click</t>
-  </si>
-  <si>
-    <t>Navigates to every link that is clicked on</t>
-  </si>
-  <si>
-    <t>Check if website works on all devices under 768px</t>
-  </si>
-  <si>
-    <t>Responds well on those screen sizes</t>
+    <t>Navigation Links</t>
+  </si>
+  <si>
+    <t>Home &gt; Early Life</t>
+  </si>
+  <si>
+    <t>Early Life page opens</t>
+  </si>
+  <si>
+    <t>Evidence</t>
   </si>
   <si>
     <t xml:space="preserve">
-The 'Gallery' link on the nav bar have disappeared to the right and the body links have been laid out into 2 rows when it went on mobile view, so these must fixed by presenting the links on the body as a column and make the nav bar links be in a form of a dropdown menu when clicked on the header on mobile view so it has space for the main page to be presented</t>
+Early Life opened up</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Home &gt; Personal Life</t>
+  </si>
+  <si>
+    <t>Personal Life page opens</t>
+  </si>
+  <si>
+    <t>Personal Life opened up</t>
+  </si>
+  <si>
+    <t>Home &gt; Skills and Qualities</t>
+  </si>
+  <si>
+    <t>Skills and Qualities opened up</t>
+  </si>
+  <si>
+    <t>Home &gt; Education</t>
+  </si>
+  <si>
+    <t>Skills and Qualities page opens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Education page page opens </t>
+  </si>
+  <si>
+    <t>Education opened up</t>
+  </si>
+  <si>
+    <t>Home &gt; Work Experience</t>
+  </si>
+  <si>
+    <t>Work Experience page opens</t>
+  </si>
+  <si>
+    <t>Work Experience opened up</t>
+  </si>
+  <si>
+    <t>Home &gt; Hobbies</t>
+  </si>
+  <si>
+    <t>Hobbies page opens up</t>
+  </si>
+  <si>
+    <t>Hobbies opened up</t>
+  </si>
+  <si>
+    <t>Home &gt; Sitemap</t>
+  </si>
+  <si>
+    <t>Sitemap page opens up</t>
+  </si>
+  <si>
+    <t>Sitemap opened up</t>
+  </si>
+  <si>
+    <t>Home &gt; Gallery</t>
+  </si>
+  <si>
+    <t>Gallery page opens up</t>
+  </si>
+  <si>
+    <t>Gallery opened up</t>
+  </si>
+  <si>
+    <t>Home refreshed</t>
+  </si>
+  <si>
+    <t>Home page refreshes</t>
+  </si>
+  <si>
+    <t>Home = Home (Refreshes)</t>
+  </si>
+  <si>
+    <t>Personal Life &gt; Work Experience</t>
+  </si>
+  <si>
+    <t>Work Experience opens from Personal Life</t>
+  </si>
+  <si>
+    <t>Work Experience &gt; Hobbies</t>
+  </si>
+  <si>
+    <t>Hobbies opens from Work Experience</t>
+  </si>
+  <si>
+    <t>Education &gt; Gallery</t>
+  </si>
+  <si>
+    <t>Gallery page opens from Education</t>
+  </si>
+  <si>
+    <t>Sitemap &gt; Early Life</t>
+  </si>
+  <si>
+    <t>Early Life opens from Sitemap</t>
+  </si>
+  <si>
+    <t>Early Life opened up</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,28 +335,28 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>148822</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>314326</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>170643</xdr:rowOff>
+      <xdr:rowOff>434105</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1654402</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2676526</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>2118134</xdr:rowOff>
+      <xdr:rowOff>1771650</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6680185B-3942-7086-FC7A-9BC2B78F05A7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42B0C8FE-9C2A-6E10-888B-069383A51762}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -163,34 +367,127 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="8871001" y="1259214"/>
-          <a:ext cx="1505580" cy="1947491"/>
+          <a:off x="11610976" y="1519955"/>
+          <a:ext cx="2362200" cy="1337545"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>6</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>7</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>8</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
+  <rel r:id="rId8"/>
+  <rel r:id="rId9"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -511,16 +808,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1BEF50-4814-4512-A0DE-435D547D7E8D}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="76.28515625" customWidth="1"/>
     <col min="3" max="3" width="45.28515625" customWidth="1"/>
     <col min="4" max="4" width="38.7109375" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="5" max="5" width="44.85546875" customWidth="1"/>
+    <col min="6" max="6" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -534,42 +832,257 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="70.5" customHeight="1">
-      <c r="A2">
-        <v>1.1000000000000001</v>
-      </c>
+    <row r="2" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="184.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="340.5" customHeight="1">
-      <c r="A3">
-        <v>1.2</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="65.25" customHeight="1">
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="169.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
+        <v>1.2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="55.5" customHeight="1">
-      <c r="A5">
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="141" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>1.4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="172.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1.5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="153.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1.6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="157.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1.7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1.8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1.9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="174.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2.1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="238.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="238.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="e" vm="9">
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
